--- a/examples/ltd-latest/expensesform.xlsx
+++ b/examples/ltd-latest/expensesform.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -170,17 +170,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="d\-mmm\-yy"/>
+    <numFmt numFmtId="166" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0.00_ ;[RED]\-0.00\ "/>
-    <numFmt numFmtId="170" formatCode="General"/>
-    <numFmt numFmtId="171" formatCode="0.00"/>
-    <numFmt numFmtId="172" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="173" formatCode="d\-mmm"/>
+    <numFmt numFmtId="170" formatCode="0.00"/>
+    <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="172" formatCode="dd\-mmm"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -462,11 +461,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -486,7 +485,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -582,11 +581,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -610,37 +609,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -713,8 +712,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -823,7 +822,7 @@
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G8" s="12"/>
     </row>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -848,6 +847,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -860,6 +860,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -1861,8 +2105,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -1984,7 +2228,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -2009,6 +2253,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -2021,6 +2266,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -3023,8 +3512,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -3146,7 +3635,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -3171,6 +3660,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -3183,6 +3673,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -4185,8 +4919,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -4308,7 +5042,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -4333,6 +5067,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -4345,6 +5080,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -5347,8 +6326,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -5473,7 +6452,7 @@
       <c r="Q7" s="49"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -5498,6 +6477,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -5510,6 +6490,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -6512,8 +7736,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -6635,7 +7859,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -6660,6 +7884,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -6672,6 +7897,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -7674,8 +9143,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -7797,7 +9266,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -7822,6 +9291,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -7834,6 +9304,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -8836,8 +10550,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -8959,7 +10673,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -8984,6 +10698,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -8996,6 +10711,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -9998,8 +11957,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -10121,7 +12080,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -10146,6 +12105,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -10158,6 +12118,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -11160,8 +13364,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -11283,7 +13487,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -11308,6 +13512,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -11320,6 +13525,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -12322,8 +14771,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -12445,7 +14894,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -12470,6 +14919,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -12482,6 +14932,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -13484,8 +16178,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW52"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.49"/>
@@ -13607,7 +16301,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" s="14" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -13632,6 +16326,7 @@
       <c r="H9" s="13" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="14" t="s">
         <v>18</v>
       </c>
@@ -13644,6 +16339,250 @@
       <c r="M9" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="14"/>
+      <c r="BX9" s="14"/>
+      <c r="BY9" s="14"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="14"/>
+      <c r="CB9" s="14"/>
+      <c r="CC9" s="14"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="14"/>
+      <c r="CF9" s="14"/>
+      <c r="CG9" s="14"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="14"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="14"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="14"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="14"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="14"/>
+      <c r="CR9" s="14"/>
+      <c r="CS9" s="14"/>
+      <c r="CT9" s="14"/>
+      <c r="CU9" s="14"/>
+      <c r="CV9" s="14"/>
+      <c r="CW9" s="14"/>
+      <c r="CX9" s="14"/>
+      <c r="CY9" s="14"/>
+      <c r="CZ9" s="14"/>
+      <c r="DA9" s="14"/>
+      <c r="DB9" s="14"/>
+      <c r="DC9" s="14"/>
+      <c r="DD9" s="14"/>
+      <c r="DE9" s="14"/>
+      <c r="DF9" s="14"/>
+      <c r="DG9" s="14"/>
+      <c r="DH9" s="14"/>
+      <c r="DI9" s="14"/>
+      <c r="DJ9" s="14"/>
+      <c r="DK9" s="14"/>
+      <c r="DL9" s="14"/>
+      <c r="DM9" s="14"/>
+      <c r="DN9" s="14"/>
+      <c r="DO9" s="14"/>
+      <c r="DP9" s="14"/>
+      <c r="DQ9" s="14"/>
+      <c r="DR9" s="14"/>
+      <c r="DS9" s="14"/>
+      <c r="DT9" s="14"/>
+      <c r="DU9" s="14"/>
+      <c r="DV9" s="14"/>
+      <c r="DW9" s="14"/>
+      <c r="DX9" s="14"/>
+      <c r="DY9" s="14"/>
+      <c r="DZ9" s="14"/>
+      <c r="EA9" s="14"/>
+      <c r="EB9" s="14"/>
+      <c r="EC9" s="14"/>
+      <c r="ED9" s="14"/>
+      <c r="EE9" s="14"/>
+      <c r="EF9" s="14"/>
+      <c r="EG9" s="14"/>
+      <c r="EH9" s="14"/>
+      <c r="EI9" s="14"/>
+      <c r="EJ9" s="14"/>
+      <c r="EK9" s="14"/>
+      <c r="EL9" s="14"/>
+      <c r="EM9" s="14"/>
+      <c r="EN9" s="14"/>
+      <c r="EO9" s="14"/>
+      <c r="EP9" s="14"/>
+      <c r="EQ9" s="14"/>
+      <c r="ER9" s="14"/>
+      <c r="ES9" s="14"/>
+      <c r="ET9" s="14"/>
+      <c r="EU9" s="14"/>
+      <c r="EV9" s="14"/>
+      <c r="EW9" s="14"/>
+      <c r="EX9" s="14"/>
+      <c r="EY9" s="14"/>
+      <c r="EZ9" s="14"/>
+      <c r="FA9" s="14"/>
+      <c r="FB9" s="14"/>
+      <c r="FC9" s="14"/>
+      <c r="FD9" s="14"/>
+      <c r="FE9" s="14"/>
+      <c r="FF9" s="14"/>
+      <c r="FG9" s="14"/>
+      <c r="FH9" s="14"/>
+      <c r="FI9" s="14"/>
+      <c r="FJ9" s="14"/>
+      <c r="FK9" s="14"/>
+      <c r="FL9" s="14"/>
+      <c r="FM9" s="14"/>
+      <c r="FN9" s="14"/>
+      <c r="FO9" s="14"/>
+      <c r="FP9" s="14"/>
+      <c r="FQ9" s="14"/>
+      <c r="FR9" s="14"/>
+      <c r="FS9" s="14"/>
+      <c r="FT9" s="14"/>
+      <c r="FU9" s="14"/>
+      <c r="FV9" s="14"/>
+      <c r="FW9" s="14"/>
+      <c r="FX9" s="14"/>
+      <c r="FY9" s="14"/>
+      <c r="FZ9" s="14"/>
+      <c r="GA9" s="14"/>
+      <c r="GB9" s="14"/>
+      <c r="GC9" s="14"/>
+      <c r="GD9" s="14"/>
+      <c r="GE9" s="14"/>
+      <c r="GF9" s="14"/>
+      <c r="GG9" s="14"/>
+      <c r="GH9" s="14"/>
+      <c r="GI9" s="14"/>
+      <c r="GJ9" s="14"/>
+      <c r="GK9" s="14"/>
+      <c r="GL9" s="14"/>
+      <c r="GM9" s="14"/>
+      <c r="GN9" s="14"/>
+      <c r="GO9" s="14"/>
+      <c r="GP9" s="14"/>
+      <c r="GQ9" s="14"/>
+      <c r="GR9" s="14"/>
+      <c r="GS9" s="14"/>
+      <c r="GT9" s="14"/>
+      <c r="GU9" s="14"/>
+      <c r="GV9" s="14"/>
+      <c r="GW9" s="14"/>
+      <c r="GX9" s="14"/>
+      <c r="GY9" s="14"/>
+      <c r="GZ9" s="14"/>
+      <c r="HA9" s="14"/>
+      <c r="HB9" s="14"/>
+      <c r="HC9" s="14"/>
+      <c r="HD9" s="14"/>
+      <c r="HE9" s="14"/>
+      <c r="HF9" s="14"/>
+      <c r="HG9" s="14"/>
+      <c r="HH9" s="14"/>
+      <c r="HI9" s="14"/>
+      <c r="HJ9" s="14"/>
+      <c r="HK9" s="14"/>
+      <c r="HL9" s="14"/>
+      <c r="HM9" s="14"/>
+      <c r="HN9" s="14"/>
+      <c r="HO9" s="14"/>
+      <c r="HP9" s="14"/>
+      <c r="HQ9" s="14"/>
+      <c r="HR9" s="14"/>
+      <c r="HS9" s="14"/>
+      <c r="HT9" s="14"/>
+      <c r="HU9" s="14"/>
+      <c r="HV9" s="14"/>
+      <c r="HW9" s="14"/>
+      <c r="HX9" s="14"/>
+      <c r="HY9" s="14"/>
+      <c r="HZ9" s="14"/>
+      <c r="IA9" s="14"/>
+      <c r="IB9" s="14"/>
+      <c r="IC9" s="14"/>
+      <c r="ID9" s="14"/>
+      <c r="IE9" s="14"/>
+      <c r="IF9" s="14"/>
+      <c r="IG9" s="14"/>
+      <c r="IH9" s="14"/>
+      <c r="II9" s="14"/>
+      <c r="IJ9" s="14"/>
+      <c r="IK9" s="14"/>
+      <c r="IL9" s="14"/>
+      <c r="IM9" s="14"/>
+      <c r="IN9" s="14"/>
+      <c r="IO9" s="14"/>
+      <c r="IP9" s="14"/>
+      <c r="IQ9" s="14"/>
+      <c r="IR9" s="14"/>
+      <c r="IS9" s="14"/>
+      <c r="IT9" s="14"/>
+      <c r="IU9" s="14"/>
+      <c r="IV9" s="14"/>
+      <c r="IW9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>

--- a/examples/ltd-latest/expensesform.xlsx
+++ b/examples/ltd-latest/expensesform.xlsx
@@ -1748,10 +1748,10 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -3154,11 +3154,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 09'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -4561,11 +4561,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 10'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -5968,11 +5968,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 11'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -7378,11 +7378,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 01'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -8785,11 +8785,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 02'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -10192,11 +10192,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 03'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -11599,11 +11599,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 04'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -13006,11 +13006,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 05'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -14413,11 +14413,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 06'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -15820,11 +15820,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 07'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
@@ -17227,11 +17227,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="str">
         <f aca="false">"Mileage Claim @ "&amp;TEXT(C30*100,0)&amp;"p"</f>
-        <v>Mileage Claim @ 45p</v>
+        <v>Mileage Claim @ 55p</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">'Month 08'!C30</f>
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM(D10:D29)</f>
